--- a/leads/High_Value_MMR_Clients.xlsx
+++ b/leads/High_Value_MMR_Clients.xlsx
@@ -659,6 +659,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -670,6 +671,7 @@
 We can help with website + capability sheet + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -754,6 +756,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -765,6 +768,7 @@
 We can help with catering website + menu packages + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -857,6 +861,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -868,6 +873,7 @@
 We can help with fix incomplete content and rebuild diabetes-clinic conversion site.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -956,6 +962,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -967,6 +974,7 @@
 We can help with full redesign + direct booking engine for landmark vashi business hotel.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1047,6 +1055,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1058,6 +1067,7 @@
 We can help with emergency full website rebuild with opd booking and department pages.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1150,6 +1160,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1161,6 +1172,7 @@
 We can help with studio website rebuild + business email + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1249,6 +1261,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1260,6 +1273,7 @@
 We can help with website refresh + consultation booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1348,6 +1362,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1359,6 +1374,7 @@
 We can help with product website + fittings catalogue + rfq. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1443,6 +1459,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1454,6 +1471,7 @@
 We can help with hospital landing + opd booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1534,6 +1552,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1545,6 +1564,7 @@
 We can help with hospital website + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1637,6 +1657,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1648,6 +1669,7 @@
 We can help with exporter website + product pages + whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1732,6 +1754,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1743,6 +1766,7 @@
 We can help with eye hospital landing + appointment. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1823,6 +1847,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1834,6 +1859,7 @@
 We can help with specialty clinic landing + booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1918,6 +1944,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -1929,6 +1956,7 @@
 We can help with authority website for cardiology/ortho/urology with package and insurance enquiry forms.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2025,6 +2053,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2036,6 +2065,7 @@
 We can help with hospital redesign + specialty pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2124,6 +2154,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2135,6 +2166,7 @@
 We can help with hospital digital redesign + tpa/enquiry ux. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2219,6 +2251,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2230,6 +2263,7 @@
 We can help with website upgrade + online booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2318,6 +2352,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2329,6 +2364,7 @@
 We can help with nexa showroom redesign + crm + offers automation. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2425,6 +2461,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2436,6 +2473,7 @@
 We can help with custom hospital site removing placeholders; iccu/ortho funnels + whatsapp booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2520,6 +2558,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2531,6 +2570,7 @@
 We can help with website + online ordering + customer crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2611,6 +2651,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2622,6 +2663,7 @@
 We can help with hospital redesign + online opd. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2706,6 +2748,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2717,6 +2760,7 @@
 We can help with modern fertility centre microsite with consult booking and outcome-trust content.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2801,6 +2845,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2812,6 +2857,7 @@
 We can help with gym website + membership enquiry + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2896,6 +2942,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2907,6 +2954,7 @@
 We can help with full hospitality brand rebuild. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -2995,6 +3043,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3006,6 +3055,7 @@
 We can help with reservation + private dining website with whatsapp and event enquiry.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3090,6 +3140,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3101,6 +3152,7 @@
 We can help with bakery website + custom cake order form + invoice later. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3181,6 +3233,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3192,6 +3245,7 @@
 We can help with order website + instagram sync. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3276,6 +3330,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3287,6 +3342,7 @@
 We can help with premium andheri dental brand site with multi-doctor profiles and booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3379,6 +3435,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3390,6 +3447,7 @@
 We can help with per-centre landing pages + whatsapp routing. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3482,6 +3540,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3493,6 +3552,7 @@
 We can help with thane centre site + scholarship/demo funnel. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3581,6 +3641,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3592,6 +3653,7 @@
 We can help with high-conversion dental brand site. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3680,6 +3742,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3691,6 +3754,7 @@
 We can help with pediatric-focused redesign with nicu/picu trust pages and parent booking cta.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3779,6 +3843,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3790,6 +3855,7 @@
 We can help with website + service booking + invoice later. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3878,6 +3944,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3889,6 +3956,7 @@
 We can help with site redesign + online booking + branch dashboard. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3985,6 +4053,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -3996,6 +4065,7 @@
 We can help with school website redesign + admissions portal ux + parent app landing. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4088,6 +4158,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4099,6 +4170,7 @@
 We can help with build clinic website + google business + whatsapp appointment system.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4183,6 +4255,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4194,6 +4267,7 @@
 We can help with dental clinic redesign + appointments. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4286,6 +4360,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4297,6 +4372,7 @@
 We can help with hospital brand rebuild + booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4389,6 +4465,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4400,6 +4477,7 @@
 We can help with studio website upgrade + business email + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4492,6 +4570,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4503,6 +4582,7 @@
 We can help with exporter website + product/spec sheets + buyer crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4599,6 +4679,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4610,6 +4691,7 @@
 We can help with complete ivf brand redesign with conversion pages and appointment automation.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4706,6 +4788,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4717,6 +4800,7 @@
 We can help with professional ivf brand site with location pages and paid-lead booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4801,6 +4885,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4812,6 +4897,7 @@
 We can help with clinic website + appointment whatsapp + reminders later. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4896,6 +4982,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4907,6 +4994,7 @@
 We can help with full redesign for hiranandani premium catchment with appointment cta.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -4991,6 +5079,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5002,6 +5091,7 @@
 We can help with hospital redesign + appointment. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5086,6 +5176,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5097,6 +5188,7 @@
 We can help with admissions ux redesign + lead routing. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5189,6 +5281,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5200,6 +5293,7 @@
 We can help with full site modernization + parts catalogue + dealer locator. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5284,6 +5378,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5295,6 +5390,7 @@
 We can help with product website + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5371,6 +5467,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5382,6 +5479,7 @@
 We can help with travel website + package pages + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5462,6 +5560,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5473,6 +5572,7 @@
 We can help with portfolio website + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5557,6 +5657,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5568,6 +5669,7 @@
 We can help with website + business email + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5652,6 +5754,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5663,6 +5766,7 @@
 We can help with site upgrade + membership crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5743,6 +5847,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5754,6 +5859,7 @@
 We can help with site upgrade + bed enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5842,6 +5948,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5853,6 +5960,7 @@
 We can help with new website + google business + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5945,6 +6053,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -5956,6 +6065,7 @@
 We can help with site upgrade + project crm + invoicing path. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6048,6 +6158,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6059,6 +6170,7 @@
 We can help with full dealer website rebuild + test-drive + service booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6151,6 +6263,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6162,6 +6275,7 @@
 We can help with panvel dealer microsite + inventory + booking crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6254,6 +6368,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6265,6 +6380,7 @@
 We can help with workshop booking portal + thane landing page. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6353,6 +6469,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6364,6 +6481,7 @@
 We can help with website redesign + lead/project crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6452,6 +6570,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6463,6 +6582,7 @@
 We can help with builder website + project lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6555,6 +6675,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6566,6 +6687,7 @@
 We can help with corporate + project website system. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6654,6 +6776,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6665,6 +6788,7 @@
 We can help with exporter website + product pages + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6753,6 +6877,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6764,6 +6889,7 @@
 We can help with website redesign + machine pages + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6856,6 +6982,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6867,6 +6994,7 @@
 We can help with unified pump website + datasheets + rfq crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6955,6 +7083,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -6966,6 +7095,7 @@
 We can help with rooms + banquet dual-funnel redesign with enquiry crm.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7054,6 +7184,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7065,6 +7196,7 @@
 We can help with 3-star hotel website rebuild with restaurant/banquet cross-sell.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7149,6 +7281,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7160,6 +7293,7 @@
 We can help with website + booking engine. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7244,6 +7378,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7255,6 +7390,7 @@
 We can help with booking-first website + google ads for station/highway travelers.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7339,6 +7475,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7350,6 +7487,7 @@
 We can help with direct booking + banquet enquiry funnel redesign.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7434,6 +7572,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7445,6 +7584,7 @@
 We can help with hotel website + whatsapp booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7541,6 +7681,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7552,6 +7693,7 @@
 We can help with modern hotel site with reservations engine and whatsapp booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7640,6 +7782,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7651,6 +7794,7 @@
 We can help with hotel redesign + booking engine. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7739,6 +7883,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7750,6 +7895,7 @@
 We can help with direct booking website + local seo for thane business travelers.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7838,6 +7984,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7849,6 +7996,7 @@
 We can help with direct booking redesign targeting midc/corporate travelers.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7937,6 +8085,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -7948,6 +8097,7 @@
 We can help with clean seafood-restaurant redesign with reservations and catering enquiry.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8032,6 +8182,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8043,6 +8194,7 @@
 We can help with booking website upgrade. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8127,6 +8279,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8138,6 +8291,7 @@
 We can help with website redesign + direct booking + business email. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8222,6 +8376,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8233,6 +8388,7 @@
 We can help with emergency website + contact cleanup and direct booking setup.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8325,6 +8481,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8336,6 +8493,7 @@
 We can help with cardiac centre website + appointment. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8432,6 +8590,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8443,6 +8602,7 @@
 We can help with multi-branch coaching website. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8539,6 +8699,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8550,6 +8711,7 @@
 We can help with premium institute website + founder brand + demo booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8642,6 +8804,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8653,6 +8816,7 @@
 We can help with website rebuild + quote calculator + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8741,6 +8905,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8752,6 +8917,7 @@
 We can help with ivf clinic brand site + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8836,6 +9002,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8847,6 +9014,7 @@
 We can help with website + capability brochure. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8923,6 +9091,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -8934,6 +9103,7 @@
 We can help with hospital website redesign. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9014,6 +9184,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9025,6 +9196,7 @@
 We can help with hospital redesign + appointment system. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9105,6 +9277,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9116,6 +9289,7 @@
 We can help with brand website + quote crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9200,6 +9374,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9211,6 +9386,7 @@
 We can help with stable dealer website rebuild + inventory + service booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9303,6 +9479,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9314,6 +9491,7 @@
 We can help with interior studio brand site + gallery crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9406,6 +9584,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9417,6 +9596,7 @@
 We can help with website modernization + datasheet library. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9505,6 +9685,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9516,6 +9697,7 @@
 We can help with hospital redesign + opd funnel. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9604,6 +9786,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9615,6 +9798,7 @@
 We can help with clean website redesign + project crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9707,6 +9891,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9718,6 +9903,7 @@
 We can help with redevelopment website + society-lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9806,6 +9992,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9817,6 +10004,7 @@
 We can help with hospital redesign + appointment crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9901,6 +10089,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9912,6 +10101,7 @@
 We can help with clinic website + online appointment + patient crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -9992,6 +10182,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10003,6 +10194,7 @@
 We can help with diagnostics website + home collection booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10095,6 +10287,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10106,6 +10299,7 @@
 We can help with studio website rebuild + business email + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10190,6 +10384,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10201,6 +10396,7 @@
 We can help with website redesign + package enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10281,6 +10477,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10292,6 +10489,7 @@
 We can help with hospital website + opd booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10384,6 +10582,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10395,6 +10594,7 @@
 We can help with ivf funnel redesign with clinic pages, cost transparency cta, and whatsapp consult booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10483,6 +10683,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10494,6 +10695,7 @@
 We can help with modern nabh-trust site with dialysis/oncology funnels and online enquiry.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10582,6 +10784,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10593,6 +10796,7 @@
 We can help with clinic website + online booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10681,6 +10885,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10692,6 +10897,7 @@
 We can help with brand website + booking + google business sync. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10780,6 +10986,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10791,6 +10998,7 @@
 We can help with exporter website + cold-chain story + buyer crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10879,6 +11087,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10890,6 +11099,7 @@
 We can help with full product website + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10974,6 +11184,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -10985,6 +11196,7 @@
 We can help with website + tooling capability pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11069,6 +11281,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11080,6 +11293,7 @@
 We can help with brand website + product catalogue. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11168,6 +11382,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11179,6 +11394,7 @@
 We can help with manufacturer catalogue site + rfq crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11271,6 +11487,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11282,6 +11499,7 @@
 We can help with exporter website redesign + product cad/spec pages + rfq crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11378,6 +11596,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11389,6 +11608,7 @@
 We can help with modern hospital website with appointment cta, doctor profiles, and google business integration.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11473,6 +11693,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11484,6 +11705,7 @@
 We can help with full website rebuild with emergency cta, maternity packages, and whatsapp booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11568,6 +11790,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11579,6 +11802,7 @@
 We can help with urgent domain recovery + new hospital website and google business overhaul.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11663,6 +11887,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11674,6 +11899,7 @@
 We can help with hospital + admissions web ux. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11754,6 +11980,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11765,6 +11992,7 @@
 We can help with hospital redesign + opd booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11849,6 +12077,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11860,6 +12089,7 @@
 We can help with owned dealer website + test-drive whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11940,6 +12170,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -11951,6 +12182,7 @@
 We can help with multi-location dealer website rebuild. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12027,6 +12259,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12038,6 +12271,7 @@
 We can help with brand website (exit aggregator dependence). If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12118,6 +12352,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12129,6 +12364,7 @@
 We can help with website + booking + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12209,6 +12445,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12220,6 +12457,7 @@
 We can help with website upgrade + lead form crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12308,6 +12546,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12319,6 +12558,7 @@
 We can help with company website + product catalogue + export crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12415,6 +12655,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12426,6 +12667,7 @@
 We can help with industrial catalogue website + rfq. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12522,6 +12764,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12533,6 +12776,7 @@
 We can help with dealer website rebuild + test-drive crm + inventory pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12629,6 +12873,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12640,6 +12885,7 @@
 We can help with dealer website modernization + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12736,6 +12982,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12747,6 +12994,7 @@
 We can help with dealer lead-gen website upgrade. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12843,6 +13091,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12854,6 +13103,7 @@
 We can help with performance site + lead attribution + whatsapp sales desk. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12950,6 +13200,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -12961,6 +13212,7 @@
 We can help with service booking portal + workshop site + whatsapp status updates. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13045,6 +13297,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13056,6 +13309,7 @@
 We can help with website + package catalogue + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13140,6 +13394,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13151,6 +13406,7 @@
 We can help with rebuild hospital site with department seo, online opd booking, and whatsapp enquiry funnel.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13239,6 +13495,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13250,6 +13507,7 @@
 We can help with portfolio website + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13334,6 +13592,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13345,6 +13604,7 @@
 We can help with lab website + test menu + home-collection form + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13433,6 +13693,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13444,6 +13705,7 @@
 We can help with company website + facility pages + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13528,6 +13790,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13539,6 +13802,7 @@
 We can help with coaching brand redesign. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13631,6 +13895,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13642,6 +13907,7 @@
 We can help with doctor-branded ivf website. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13726,6 +13992,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13737,6 +14004,7 @@
 We can help with site refresh + online slot booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13821,6 +14089,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13832,6 +14101,7 @@
 We can help with website + whatsapp catalogue + quote form. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13916,6 +14186,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -13927,6 +14198,7 @@
 We can help with coaching site + admission crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14015,6 +14287,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14026,6 +14299,7 @@
 We can help with website + catalogue + lead inbox. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14118,6 +14392,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14129,6 +14404,7 @@
 We can help with hospital website rebuild + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14221,6 +14497,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14232,6 +14509,7 @@
 We can help with facility website + capacity enquiry + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14320,6 +14598,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14331,6 +14610,7 @@
 We can help with clean rebuild, correct contact stack, google reviews, and whatsapp appointments.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14419,6 +14699,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14430,6 +14711,7 @@
 We can help with admissions-focused website + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14522,6 +14804,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14533,6 +14816,7 @@
 We can help with course-led redesign + test series funnel + whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14617,6 +14901,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14628,6 +14913,7 @@
 We can help with hospital group digital redesign. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14712,6 +14998,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14723,6 +15010,7 @@
 We can help with site refresh + crm for pharma rfqs. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14819,6 +15107,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14830,6 +15119,7 @@
 We can help with pharma equipment website + business email + rfq crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14918,6 +15208,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -14929,6 +15220,7 @@
 We can help with manufacturing solutions website + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15021,6 +15313,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15032,6 +15325,7 @@
 We can help with clean ivf rebuild, remove stale content, add enquiry + whatsapp cta.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15112,6 +15406,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15123,6 +15418,7 @@
 We can help with restaurant website + menu + reservation whatsapp. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15215,6 +15511,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15226,6 +15523,7 @@
 We can help with hospital brand redesign + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15314,6 +15612,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15325,6 +15624,7 @@
 We can help with hospital website modernization. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15413,6 +15713,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15424,6 +15725,7 @@
 We can help with https redesign + portfolio + quote crm + invoice later. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15508,6 +15810,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15519,6 +15822,7 @@
 We can help with website redesign + booking enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15603,6 +15907,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15614,6 +15919,7 @@
 We can help with engineering website + datasheets + rfq. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15702,6 +16008,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15713,6 +16020,7 @@
 We can help with sanpada showroom site + test-drive whatsapp desk. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15805,6 +16113,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15816,6 +16125,7 @@
 We can help with owned dealer website + lead crm + offers engine. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15912,6 +16222,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -15923,6 +16234,7 @@
 We can help with clinical rebrand site for icu/heart/diabetes with appointment and package ctas.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16011,6 +16323,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16022,6 +16335,7 @@
 We can help with custom website + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16106,6 +16420,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16117,6 +16432,7 @@
 We can help with hospital website redesign + appointment + department pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16201,6 +16517,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16212,6 +16529,7 @@
 We can help with website + conveyor product pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16300,6 +16618,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16311,6 +16630,7 @@
 We can help with hospital group website + local landing. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16399,6 +16719,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16410,6 +16731,7 @@
 We can help with hospital ux modernization + appointment funnel. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16494,6 +16816,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16505,6 +16828,7 @@
 We can help with hospital brand website + appointment. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16589,6 +16913,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16600,6 +16925,7 @@
 We can help with website + instant quote form + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16696,6 +17022,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16707,6 +17034,7 @@
 We can help with hospital website modernization. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16795,6 +17123,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16806,6 +17135,7 @@
 We can help with brand website + service booking + invoice later. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16894,6 +17224,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16905,6 +17236,7 @@
 We can help with full website redesign + product specs + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -16993,6 +17325,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17004,6 +17337,7 @@
 We can help with hospital redesign + specialty pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17088,6 +17422,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17099,6 +17434,7 @@
 We can help with guest house website + direct booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17183,6 +17519,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17194,6 +17531,7 @@
 We can help with website + company email. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17290,6 +17628,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17301,6 +17640,7 @@
 We can help with full dealer site rebuild + oem-compliant ux + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17393,6 +17733,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17404,6 +17745,7 @@
 We can help with service booking microsite + whatsapp service desk. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17496,6 +17838,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17507,6 +17850,7 @@
 We can help with dealer redesign + ev content + test-drive crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17603,6 +17947,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17614,6 +17959,7 @@
 We can help with cardiac hospital brand site + appointment. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17698,6 +18044,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17709,6 +18056,7 @@
 We can help with hospital website modernization. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17793,6 +18141,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17804,6 +18153,7 @@
 We can help with admissions website optimization + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17892,6 +18242,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17903,6 +18254,7 @@
 We can help with nexa-grade website + booking crm + inventory ux. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -17995,6 +18347,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18006,6 +18359,7 @@
 We can help with group dealer website + outlet pages + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18102,6 +18456,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18113,6 +18468,7 @@
 We can help with premium dental brand refresh with invisalign/implant funnels and dual-clinic booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18197,6 +18553,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18208,6 +18565,7 @@
 We can help with website refresh + online appointments. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18296,6 +18654,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18307,6 +18666,7 @@
 We can help with exporter website + certifications page + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18395,6 +18755,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18406,6 +18767,7 @@
 We can help with website + capability brochure + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18494,6 +18856,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18505,6 +18868,7 @@
 We can help with website rebuild + business email + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18597,6 +18961,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18608,6 +18973,7 @@
 We can help with brand-site redesign + business email + quote crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18704,6 +19070,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18715,6 +19082,7 @@
 We can help with hospital website + opd booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18807,6 +19175,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18818,6 +19187,7 @@
 We can help with developer site redesign + project pages + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18910,6 +19280,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -18921,6 +19292,7 @@
 We can help with full redesign + branch pages + admissions crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19017,6 +19389,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19028,6 +19401,7 @@
 We can help with modern clinic website with implant/rct packages and whatsapp booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19116,6 +19490,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19127,6 +19502,7 @@
 We can help with custom domain website + business email + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19211,6 +19587,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19222,6 +19599,7 @@
 We can help with website + rfq form. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19302,6 +19680,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19313,6 +19692,7 @@
 We can help with maternity + ivf redesign. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19401,6 +19781,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19412,6 +19793,7 @@
 We can help with redesign with mobile booking, whatsapp opd, and specialty service pages.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19508,6 +19890,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19519,6 +19902,7 @@
 We can help with dental clinic redesign with implant/invisalign funnels and online booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19607,6 +19991,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19618,6 +20003,7 @@
 We can help with finish brand site, add table booking and events/parties funnel.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19710,6 +20096,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19721,6 +20108,7 @@
 We can help with premium preschool brand site + tour booking + whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19809,6 +20197,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19820,6 +20209,7 @@
 We can help with hotel redesign + booking engine. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19908,6 +20298,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19919,6 +20310,7 @@
 We can help with corporate website + product catalogue + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -19999,6 +20391,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20010,6 +20403,7 @@
 We can help with premium hospital website + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20098,6 +20492,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20109,6 +20504,7 @@
 We can help with company website + product crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20197,6 +20593,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20208,6 +20605,7 @@
 We can help with export brand website + buyer portal + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20296,6 +20694,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20307,6 +20706,7 @@
 We can help with rebuild restaurant/lounge site with reservations and banquet enquiry.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20395,6 +20795,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20406,6 +20807,7 @@
 We can help with portfolio redesign + project enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20498,6 +20900,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20509,6 +20912,7 @@
 We can help with site refresh + online enquiry + student crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20601,6 +21005,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20612,6 +21017,7 @@
 We can help with full website redesign + quote crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20708,6 +21114,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20719,6 +21126,7 @@
 We can help with counsellor dashboard + whatsapp admissions + fee enquiry automation. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20803,6 +21211,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20814,6 +21223,7 @@
 We can help with website + parts catalogue. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20898,6 +21308,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20909,6 +21320,7 @@
 We can help with ivf landing + whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -20993,6 +21405,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21004,6 +21417,7 @@
 We can help with local vashi/thane ivf brand polish + whatsapp and paid-lead landing pages.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21092,6 +21506,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21103,6 +21518,7 @@
 We can help with multi-property booking site with ota-independent reservations.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21195,6 +21611,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21206,6 +21623,7 @@
 We can help with portfolio redesign + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21290,6 +21708,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21301,6 +21720,7 @@
 We can help with diagnostics brand rebuild. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21389,6 +21809,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21400,6 +21821,7 @@
 We can help with ui/ux polish + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21492,6 +21914,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21503,6 +21926,7 @@
 We can help with local centre microsite overlay + lead capture upgrade. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21599,6 +22023,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21610,6 +22035,7 @@
 We can help with premium admissions experience redesign + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21698,6 +22124,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21709,6 +22136,7 @@
 We can help with interior brand redesign + lead form. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21797,6 +22225,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21808,6 +22237,7 @@
 We can help with centre microsites + whatsapp admissions crm + demo booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21900,6 +22330,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -21911,6 +22342,7 @@
 We can help with kharghar centre site + google business + whatsapp lead desk. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22003,6 +22435,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22014,6 +22447,7 @@
 We can help with gb road landing + batch comparison + lead scoring crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22106,6 +22540,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22117,6 +22552,7 @@
 We can help with mulund centre site + counsellor booking calendar. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22209,6 +22645,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22220,6 +22657,7 @@
 We can help with nerul landing page + asat/demo booking + parent whatsapp. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22312,6 +22750,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22323,6 +22762,7 @@
 We can help with panvel microsite + map seo + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22415,6 +22855,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22426,6 +22867,7 @@
 We can help with local seo landing page + batch enquiry form + call tracking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22514,6 +22956,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22525,6 +22968,7 @@
 We can help with client crm + filing dashboard. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22609,6 +23053,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22620,6 +23065,7 @@
 We can help with diagnostics website + booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22708,6 +23154,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22719,6 +23166,7 @@
 We can help with brand-site refresh + business email + booking crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22811,6 +23259,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22822,6 +23271,7 @@
 We can help with custom portfolio site + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22906,6 +23356,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -22917,6 +23368,7 @@
 We can help with admissions ux upgrade + whatsapp counsellor flow. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23001,6 +23453,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23012,6 +23465,7 @@
 We can help with campus site polish + admissions crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23100,6 +23554,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23111,6 +23566,7 @@
 We can help with dealer redesign + test-drive crm + inventory seo. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23203,6 +23659,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23214,6 +23671,7 @@
 We can help with location landing + offers funnel + whatsapp sales. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23306,6 +23764,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23317,6 +23776,7 @@
 We can help with online service booking + status crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23409,6 +23869,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23420,6 +23881,7 @@
 We can help with project-led website redesign + whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23516,6 +23978,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23527,6 +23990,7 @@
 We can help with capability website + service booking + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23611,6 +24075,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23622,6 +24087,7 @@
 We can help with diagnostics centre website + booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23714,6 +24180,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23725,6 +24192,7 @@
 We can help with product-led website refresh + rfq crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23809,6 +24277,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23820,6 +24289,7 @@
 We can help with hospital website + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23904,6 +24374,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -23915,6 +24386,7 @@
 We can help with table booking + catering/events landing pages.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24007,6 +24479,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24018,6 +24491,7 @@
 We can help with add email/crm, stronger implant cta, and google ads landing pages.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24102,6 +24576,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24113,6 +24588,7 @@
 We can help with online join + member dashboard. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24205,6 +24681,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24216,6 +24693,7 @@
 We can help with campus microsite + admissions whatsapp + tour scheduler. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24304,6 +24782,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24315,6 +24794,7 @@
 We can help with group website redesign + project crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24395,6 +24875,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24406,6 +24887,7 @@
 We can help with clinic website + appointment booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24486,6 +24968,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24497,6 +24980,7 @@
 We can help with belapur outlet landing page with direct orders and table booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24581,6 +25065,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24592,6 +25077,7 @@
 We can help with clear contact redesign + whatsapp/opd booking and specialty pages.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24680,6 +25166,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24691,6 +25178,7 @@
 We can help with hotel website + whatsapp booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24779,6 +25267,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24790,6 +25279,7 @@
 We can help with hotel website + direct booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24878,6 +25368,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24889,6 +25380,7 @@
 We can help with hotel redesign + online reservation. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24981,6 +25473,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -24992,6 +25485,7 @@
 We can help with conversion ux upgrade + consultation crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25084,6 +25578,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25095,6 +25590,7 @@
 We can help with kharghar centre page + results showcase + lead form. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25187,6 +25683,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25198,6 +25695,7 @@
 We can help with thane-specific landing + demo booking crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25290,6 +25788,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25301,6 +25800,7 @@
 We can help with ulwe centre microsite + counsellor whatsapp + test booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25397,6 +25897,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25408,6 +25909,7 @@
 We can help with portfolio website redesign + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25496,6 +25998,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25507,6 +26010,7 @@
 We can help with plant capability website + capacity calculator + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25587,6 +26091,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25598,6 +26103,7 @@
 We can help with booking upgrade + guest crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25678,6 +26184,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25689,6 +26196,7 @@
 We can help with public opd ux modernization. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25777,6 +26285,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25788,6 +26297,7 @@
 We can help with implant/full-mouth rehab landing pages + crm booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25872,6 +26382,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25883,6 +26394,7 @@
 We can help with local thane campaign pages + specialty lead capture optimization.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25979,6 +26491,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -25990,6 +26503,7 @@
 We can help with developer website redesign + project microsites + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26082,6 +26596,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26093,6 +26608,7 @@
 We can help with facility website + capacity booking + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26185,6 +26701,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26196,6 +26713,7 @@
 We can help with site modernization + business email + buyer crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26288,6 +26806,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26299,6 +26818,7 @@
 We can help with catalogue website upgrade + bulk-quote crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26391,6 +26911,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26402,6 +26923,7 @@
 We can help with website upgrade + project crm + redevelopment funnel. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26486,6 +27008,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26497,6 +27020,7 @@
 We can help with owned ordering + reservations site to reduce aggregator dependence.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26589,6 +27113,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26600,6 +27125,7 @@
 We can help with seals catalogue website + seo + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26684,6 +27210,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26695,6 +27222,7 @@
 We can help with lab brand website + home collection. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26779,6 +27307,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26790,6 +27319,7 @@
 We can help with ux refresh focused on opd booking, specialty landing pages, and lead capture.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26886,6 +27416,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26897,6 +27428,7 @@
 We can help with interior portfolio site + whatsapp leads. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26985,6 +27517,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -26996,6 +27529,7 @@
 We can help with local seo site with whatsapp ordering and table reservation cta.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27092,6 +27626,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27103,6 +27638,7 @@
 We can help with service booking website + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27199,6 +27735,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27210,6 +27747,7 @@
 We can help with portfolio redesign + consultation booking crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27294,6 +27832,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27305,6 +27844,7 @@
 We can help with hospital website redesign. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27389,6 +27929,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27400,6 +27941,7 @@
 We can help with direct-order website to cut swiggy/zomato commissions.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27496,6 +28038,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27507,6 +28050,7 @@
 We can help with diagnostics centre website + booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27595,6 +28139,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27606,6 +28151,7 @@
 We can help with multi-centre coaching website + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27702,6 +28248,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27713,6 +28260,7 @@
 We can help with direct booking + events/f&amp;b lead funnels for premium thane property.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27809,6 +28357,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27820,6 +28369,7 @@
 We can help with board-specific campus sites + admissions crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27916,6 +28466,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -27927,6 +28478,7 @@
 We can help with school ops portal + website cms upgrade. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28023,6 +28575,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28034,6 +28587,7 @@
 We can help with campus-led redesign + counsellor booking + parent portal landing. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28118,6 +28672,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28129,6 +28684,7 @@
 We can help with patient-facing hospital website. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28217,6 +28773,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28228,6 +28785,7 @@
 We can help with unified developer website + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28312,6 +28870,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28323,6 +28882,7 @@
 We can help with clinic website cleanup + booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28407,6 +28967,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28418,6 +28979,7 @@
 We can help with online quote + job crm + invoicing. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28506,6 +29068,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28517,6 +29080,7 @@
 We can help with admissions crm + booking ux. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28605,6 +29169,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28616,6 +29181,7 @@
 We can help with modern clinic site + whatsapp booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28708,6 +29274,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28719,6 +29286,7 @@
 We can help with facility website + capacity enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28815,6 +29383,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28826,6 +29395,7 @@
 We can help with high-end smile makeover funnel with before/after and consult booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28910,6 +29480,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -28921,6 +29492,7 @@
 We can help with brand site with menu, whatsapp pre-orders, and local seo.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29009,6 +29581,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29020,6 +29593,7 @@
 We can help with school brand refresh + admissions funnel + virtual tour ux. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29108,6 +29682,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29119,6 +29694,7 @@
 We can help with campus-led redesign + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29207,6 +29783,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29218,6 +29795,7 @@
 We can help with admissions microsite + counsellor whatsapp + campus media. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29302,6 +29880,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29313,6 +29892,7 @@
 We can help with online quote + lead dashboard. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29401,6 +29981,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29412,6 +29993,7 @@
 We can help with exporter site refresh + domain email + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29504,6 +30086,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29515,6 +30098,7 @@
 We can help with property crm + listing dashboard + site upgrade. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29607,6 +30191,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29618,6 +30203,7 @@
 We can help with corporate redesign + project case studies + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29714,6 +30300,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29725,6 +30312,7 @@
 We can help with packaging website + catalogue + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29817,6 +30405,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29828,6 +30417,7 @@
 We can help with brand-site refresh + business email + buyer crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29924,6 +30514,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -29935,6 +30526,7 @@
 We can help with portfolio website upgrade + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30031,6 +30623,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30042,6 +30635,7 @@
 We can help with architecture studio redesign + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30126,6 +30720,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30137,6 +30732,7 @@
 We can help with hospital website rebuild + modern email. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30221,6 +30817,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30232,6 +30829,7 @@
 We can help with specialty seo hubs + appointment automation for high-intent opd leads.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30324,6 +30922,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30335,6 +30934,7 @@
 We can help with project website system + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30431,6 +31031,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30442,6 +31043,7 @@
 We can help with admissions funnel cleanup + school site cro + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30530,6 +31132,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30541,6 +31144,7 @@
 We can help with property microsite upgrade with direct booking and corporate enquiry forms.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30633,6 +31237,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30644,6 +31249,7 @@
 We can help with exporter website + product skus + buyer crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30728,6 +31334,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30739,6 +31346,7 @@
 We can help with coaching website + whatsapp admissions. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30827,6 +31435,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30838,6 +31447,7 @@
 We can help with toyota dealer ux refresh + outlet pages + booking crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30926,6 +31536,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -30937,6 +31548,7 @@
 We can help with service booking portal + workshop landing. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -31792,6 +32404,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -31803,6 +32416,7 @@
 We can help with website + capability sheet + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -31849,6 +32463,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -31860,6 +32475,7 @@
 We can help with catering website + menu packages + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -31906,6 +32522,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -31917,6 +32534,7 @@
 We can help with fix incomplete content and rebuild diabetes-clinic conversion site.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -31963,6 +32581,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32014,6 +32633,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32025,6 +32645,7 @@
 We can help with emergency full website rebuild with opd booking and department pages.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32071,6 +32692,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32082,6 +32704,7 @@
 We can help with studio website rebuild + business email + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32128,6 +32751,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32139,6 +32763,7 @@
 We can help with website refresh + consultation booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32185,6 +32810,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32196,6 +32822,7 @@
 We can help with product website + fittings catalogue + rfq. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32238,6 +32865,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32285,6 +32913,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32336,6 +32965,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32347,6 +32977,7 @@
 We can help with exporter website + product pages + whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32389,6 +33020,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32436,6 +33068,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32487,6 +33120,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32498,6 +33132,7 @@
 We can help with authority website for cardiology/ortho/urology with package and insurance enquiry forms.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32544,6 +33179,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32555,6 +33191,7 @@
 We can help with hospital redesign + specialty pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32601,6 +33238,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32612,6 +33250,7 @@
 We can help with hospital digital redesign + tpa/enquiry ux. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32658,6 +33297,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32669,6 +33309,7 @@
 We can help with website upgrade + online booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32715,6 +33356,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32726,6 +33368,7 @@
 We can help with nexa showroom redesign + crm + offers automation. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32772,6 +33415,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32783,6 +33427,7 @@
 We can help with custom hospital site removing placeholders; iccu/ortho funnels + whatsapp booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32829,6 +33474,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32840,6 +33486,7 @@
 We can help with website + online ordering + customer crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32886,6 +33533,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32897,6 +33545,7 @@
 We can help with hospital redesign + online opd. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32943,6 +33592,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -32954,6 +33604,7 @@
 We can help with modern fertility centre microsite with consult booking and outcome-trust content.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33000,6 +33651,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33011,6 +33663,7 @@
 We can help with gym website + membership enquiry + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33057,6 +33710,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33068,6 +33722,7 @@
 We can help with full hospitality brand rebuild. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33114,6 +33769,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33125,6 +33781,7 @@
 We can help with reservation + private dining website with whatsapp and event enquiry.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33171,6 +33828,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33182,6 +33840,7 @@
 We can help with bakery website + custom cake order form + invoice later. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33228,6 +33887,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33239,6 +33899,7 @@
 We can help with order website + instagram sync. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33285,6 +33946,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33296,6 +33958,7 @@
 We can help with premium andheri dental brand site with multi-doctor profiles and booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33342,6 +34005,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33353,6 +34017,7 @@
 We can help with per-centre landing pages + whatsapp routing. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33399,6 +34064,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33410,6 +34076,7 @@
 We can help with thane centre site + scholarship/demo funnel. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33456,6 +34123,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33467,6 +34135,7 @@
 We can help with high-conversion dental brand site. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33513,6 +34182,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33564,6 +34234,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33575,6 +34246,7 @@
 We can help with website + service booking + invoice later. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33621,6 +34293,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33632,6 +34305,7 @@
 We can help with site redesign + online booking + branch dashboard. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33678,6 +34352,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33729,6 +34404,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33740,6 +34416,7 @@
 We can help with build clinic website + google business + whatsapp appointment system.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33786,6 +34463,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33797,6 +34475,7 @@
 We can help with dental clinic redesign + appointments. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33843,6 +34522,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33854,6 +34534,7 @@
 We can help with hospital brand rebuild + booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33900,6 +34581,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33911,6 +34593,7 @@
 We can help with studio website upgrade + business email + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33957,6 +34640,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -33968,6 +34652,7 @@
 We can help with exporter website + product/spec sheets + buyer crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34014,6 +34699,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34025,6 +34711,7 @@
 We can help with complete ivf brand redesign with conversion pages and appointment automation.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34071,6 +34758,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34082,6 +34770,7 @@
 We can help with professional ivf brand site with location pages and paid-lead booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34128,6 +34817,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34139,6 +34829,7 @@
 We can help with clinic website + appointment whatsapp + reminders later. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34185,6 +34876,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34196,6 +34888,7 @@
 We can help with full redesign for hiranandani premium catchment with appointment cta.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34238,6 +34931,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34289,6 +34983,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34300,6 +34995,7 @@
 We can help with admissions ux redesign + lead routing. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34346,6 +35042,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34357,6 +35054,7 @@
 We can help with full site modernization + parts catalogue + dealer locator. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34403,6 +35101,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34454,6 +35153,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34465,6 +35165,7 @@
 We can help with travel website + package pages + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34511,6 +35212,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34522,6 +35224,7 @@
 We can help with portfolio website + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34568,6 +35271,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34579,6 +35283,7 @@
 We can help with website + business email + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34625,6 +35330,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34636,6 +35342,7 @@
 We can help with site upgrade + membership crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34682,6 +35389,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34693,6 +35401,7 @@
 We can help with site upgrade + bed enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34739,6 +35448,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34750,6 +35460,7 @@
 We can help with new website + google business + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34796,6 +35507,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34807,6 +35519,7 @@
 We can help with site upgrade + project crm + invoicing path. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34853,6 +35566,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34864,6 +35578,7 @@
 We can help with full dealer website rebuild + test-drive + service booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34910,6 +35625,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34921,6 +35637,7 @@
 We can help with panvel dealer microsite + inventory + booking crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34967,6 +35684,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -34978,6 +35696,7 @@
 We can help with workshop booking portal + thane landing page. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35024,6 +35743,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35035,6 +35755,7 @@
 We can help with website redesign + lead/project crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35081,6 +35802,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35132,6 +35854,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35183,6 +35906,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35194,6 +35918,7 @@
 We can help with exporter website + product pages + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35240,6 +35965,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35251,6 +35977,7 @@
 We can help with website redesign + machine pages + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35297,6 +36024,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35308,6 +36036,7 @@
 We can help with unified pump website + datasheets + rfq crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35354,6 +36083,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35365,6 +36095,7 @@
 We can help with rooms + banquet dual-funnel redesign with enquiry crm.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35411,6 +36142,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35422,6 +36154,7 @@
 We can help with 3-star hotel website rebuild with restaurant/banquet cross-sell.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35468,6 +36201,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35479,6 +36213,7 @@
 We can help with website + booking engine. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35525,6 +36260,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35536,6 +36272,7 @@
 We can help with booking-first website + google ads for station/highway travelers.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35582,6 +36319,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35593,6 +36331,7 @@
 We can help with direct booking + banquet enquiry funnel redesign.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35639,6 +36378,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35650,6 +36390,7 @@
 We can help with hotel website + whatsapp booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35696,6 +36437,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35707,6 +36449,7 @@
 We can help with modern hotel site with reservations engine and whatsapp booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35753,6 +36496,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35764,6 +36508,7 @@
 We can help with hotel redesign + booking engine. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35810,6 +36555,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35821,6 +36567,7 @@
 We can help with direct booking website + local seo for thane business travelers.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35867,6 +36614,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35878,6 +36626,7 @@
 We can help with direct booking redesign targeting midc/corporate travelers.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35924,6 +36673,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35935,6 +36685,7 @@
 We can help with clean seafood-restaurant redesign with reservations and catering enquiry.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35981,6 +36732,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -35992,6 +36744,7 @@
 We can help with booking website upgrade. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36038,6 +36791,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36049,6 +36803,7 @@
 We can help with website redesign + direct booking + business email. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36095,6 +36850,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36106,6 +36862,7 @@
 We can help with emergency website + contact cleanup and direct booking setup.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36152,6 +36909,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36163,6 +36921,7 @@
 We can help with cardiac centre website + appointment. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36209,6 +36968,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36220,6 +36980,7 @@
 We can help with multi-branch coaching website. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36266,6 +37027,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36277,6 +37039,7 @@
 We can help with premium institute website + founder brand + demo booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36323,6 +37086,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36334,6 +37098,7 @@
 We can help with website rebuild + quote calculator + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36380,6 +37145,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36391,6 +37157,7 @@
 We can help with ivf clinic brand site + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36437,6 +37204,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36484,6 +37252,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36531,6 +37300,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36582,6 +37352,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36593,6 +37364,7 @@
 We can help with brand website + quote crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36639,6 +37411,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36650,6 +37423,7 @@
 We can help with stable dealer website rebuild + inventory + service booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36696,6 +37470,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36707,6 +37482,7 @@
 We can help with interior studio brand site + gallery crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36753,6 +37529,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36764,6 +37541,7 @@
 We can help with website modernization + datasheet library. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36810,6 +37588,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36821,6 +37600,7 @@
 We can help with hospital redesign + opd funnel. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36867,6 +37647,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36878,6 +37659,7 @@
 We can help with clean website redesign + project crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36924,6 +37706,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36935,6 +37718,7 @@
 We can help with redevelopment website + society-lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36981,6 +37765,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -36992,6 +37777,7 @@
 We can help with hospital redesign + appointment crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37038,6 +37824,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37049,6 +37836,7 @@
 We can help with clinic website + online appointment + patient crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37091,6 +37879,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37142,6 +37931,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37153,6 +37943,7 @@
 We can help with studio website rebuild + business email + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37199,6 +37990,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37210,6 +38002,7 @@
 We can help with website redesign + package enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37252,6 +38045,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37303,6 +38097,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37314,6 +38109,7 @@
 We can help with ivf funnel redesign with clinic pages, cost transparency cta, and whatsapp consult booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37360,6 +38156,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37371,6 +38168,7 @@
 We can help with modern nabh-trust site with dialysis/oncology funnels and online enquiry.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37417,6 +38215,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37428,6 +38227,7 @@
 We can help with clinic website + online booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37474,6 +38274,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37485,6 +38286,7 @@
 We can help with brand website + booking + google business sync. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37531,6 +38333,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37542,6 +38345,7 @@
 We can help with exporter website + cold-chain story + buyer crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37588,6 +38392,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37599,6 +38404,7 @@
 We can help with full product website + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37645,6 +38451,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37656,6 +38463,7 @@
 We can help with website + tooling capability pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37702,6 +38510,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37713,6 +38522,7 @@
 We can help with brand website + product catalogue. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37759,6 +38569,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37810,6 +38621,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37821,6 +38633,7 @@
 We can help with exporter website redesign + product cad/spec pages + rfq crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37867,6 +38680,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37878,6 +38692,7 @@
 We can help with modern hospital website with appointment cta, doctor profiles, and google business integration.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37924,6 +38739,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37935,6 +38751,7 @@
 We can help with full website rebuild with emergency cta, maternity packages, and whatsapp booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37981,6 +38798,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -37992,6 +38810,7 @@
 We can help with urgent domain recovery + new hospital website and google business overhaul.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38034,6 +38853,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38081,6 +38901,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38132,6 +38953,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38143,6 +38965,7 @@
 We can help with owned dealer website + test-drive whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38189,6 +39012,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38240,6 +39064,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38251,6 +39076,7 @@
 We can help with brand website (exit aggregator dependence). If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38297,6 +39123,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38308,6 +39135,7 @@
 We can help with website + booking + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38354,6 +39182,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38365,6 +39194,7 @@
 We can help with website upgrade + lead form crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38411,6 +39241,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38422,6 +39253,7 @@
 We can help with company website + product catalogue + export crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38468,6 +39300,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38479,6 +39312,7 @@
 We can help with industrial catalogue website + rfq. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38525,6 +39359,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38536,6 +39371,7 @@
 We can help with dealer website rebuild + test-drive crm + inventory pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38582,6 +39418,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38593,6 +39430,7 @@
 We can help with dealer website modernization + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38639,6 +39477,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38650,6 +39489,7 @@
 We can help with dealer lead-gen website upgrade. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38696,6 +39536,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38707,6 +39548,7 @@
 We can help with performance site + lead attribution + whatsapp sales desk. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38753,6 +39595,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38764,6 +39607,7 @@
 We can help with service booking portal + workshop site + whatsapp status updates. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38810,6 +39654,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38821,6 +39666,7 @@
 We can help with website + package catalogue + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38867,6 +39713,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38878,6 +39725,7 @@
 We can help with rebuild hospital site with department seo, online opd booking, and whatsapp enquiry funnel.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38924,6 +39772,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38935,6 +39784,7 @@
 We can help with portfolio website + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38981,6 +39831,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -38992,6 +39843,7 @@
 We can help with lab website + test menu + home-collection form + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39034,6 +39886,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39085,6 +39938,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39096,6 +39950,7 @@
 We can help with coaching brand redesign. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39142,6 +39997,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39153,6 +40009,7 @@
 We can help with doctor-branded ivf website. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39199,6 +40056,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39210,6 +40068,7 @@
 We can help with site refresh + online slot booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39256,6 +40115,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39267,6 +40127,7 @@
 We can help with website + whatsapp catalogue + quote form. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39313,6 +40174,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39324,6 +40186,7 @@
 We can help with coaching site + admission crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39370,6 +40233,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39381,6 +40245,7 @@
 We can help with website + catalogue + lead inbox. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39427,6 +40292,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39438,6 +40304,7 @@
 We can help with hospital website rebuild + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39484,6 +40351,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39495,6 +40363,7 @@
 We can help with facility website + capacity enquiry + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39541,6 +40410,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39552,6 +40422,7 @@
 We can help with clean rebuild, correct contact stack, google reviews, and whatsapp appointments.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39598,6 +40469,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39609,6 +40481,7 @@
 We can help with admissions-focused website + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39655,6 +40528,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39666,6 +40540,7 @@
 We can help with course-led redesign + test series funnel + whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39708,6 +40583,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39759,6 +40635,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39770,6 +40647,7 @@
 We can help with site refresh + crm for pharma rfqs. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39816,6 +40694,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39827,6 +40706,7 @@
 We can help with pharma equipment website + business email + rfq crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39873,6 +40753,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39884,6 +40765,7 @@
 We can help with manufacturing solutions website + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39930,6 +40812,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39941,6 +40824,7 @@
 We can help with clean ivf rebuild, remove stale content, add enquiry + whatsapp cta.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39987,6 +40871,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -39998,6 +40883,7 @@
 We can help with restaurant website + menu + reservation whatsapp. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40044,6 +40930,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40055,6 +40942,7 @@
 We can help with hospital brand redesign + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40101,6 +40989,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40112,6 +41001,7 @@
 We can help with hospital website modernization. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40158,6 +41048,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40169,6 +41060,7 @@
 We can help with https redesign + portfolio + quote crm + invoice later. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40215,6 +41107,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40226,6 +41119,7 @@
 We can help with website redesign + booking enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40272,6 +41166,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40283,6 +41178,7 @@
 We can help with engineering website + datasheets + rfq. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40329,6 +41225,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40340,6 +41237,7 @@
 We can help with sanpada showroom site + test-drive whatsapp desk. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40386,6 +41284,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40397,6 +41296,7 @@
 We can help with owned dealer website + lead crm + offers engine. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40443,6 +41343,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40454,6 +41355,7 @@
 We can help with clinical rebrand site for icu/heart/diabetes with appointment and package ctas.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40500,6 +41402,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40511,6 +41414,7 @@
 We can help with custom website + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40557,6 +41461,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40568,6 +41473,7 @@
 We can help with hospital website redesign + appointment + department pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40614,6 +41520,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40625,6 +41532,7 @@
 We can help with website + conveyor product pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40671,6 +41579,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40682,6 +41591,7 @@
 We can help with hospital group website + local landing. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40728,6 +41638,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40739,6 +41650,7 @@
 We can help with hospital ux modernization + appointment funnel. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40781,6 +41693,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40832,6 +41745,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40843,6 +41757,7 @@
 We can help with website + instant quote form + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40889,6 +41804,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40900,6 +41816,7 @@
 We can help with hospital website modernization. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40946,6 +41863,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -40957,6 +41875,7 @@
 We can help with brand website + service booking + invoice later. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41003,6 +41922,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41014,6 +41934,7 @@
 We can help with full website redesign + product specs + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41060,6 +41981,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41071,6 +41993,7 @@
 We can help with hospital redesign + specialty pages. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41117,6 +42040,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41128,6 +42052,7 @@
 We can help with guest house website + direct booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41174,6 +42099,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41185,6 +42111,7 @@
 We can help with website + company email. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41231,6 +42158,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41242,6 +42170,7 @@
 We can help with full dealer site rebuild + oem-compliant ux + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41288,6 +42217,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41299,6 +42229,7 @@
 We can help with service booking microsite + whatsapp service desk. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41345,6 +42276,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41356,6 +42288,7 @@
 We can help with dealer redesign + ev content + test-drive crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41402,6 +42335,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41413,6 +42347,7 @@
 We can help with cardiac hospital brand site + appointment. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41455,6 +42390,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41506,6 +42442,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41557,6 +42494,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41568,6 +42506,7 @@
 We can help with nexa-grade website + booking crm + inventory ux. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41614,6 +42553,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41625,6 +42565,7 @@
 We can help with group dealer website + outlet pages + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41671,6 +42612,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41682,6 +42624,7 @@
 We can help with premium dental brand refresh with invisalign/implant funnels and dual-clinic booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41728,6 +42671,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41739,6 +42683,7 @@
 We can help with website refresh + online appointments. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41785,6 +42730,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41796,6 +42742,7 @@
 We can help with exporter website + certifications page + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41842,6 +42789,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41853,6 +42801,7 @@
 We can help with website + capability brochure + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41899,6 +42848,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41910,6 +42860,7 @@
 We can help with website rebuild + business email + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41956,6 +42907,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -41967,6 +42919,7 @@
 We can help with brand-site redesign + business email + quote crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42013,6 +42966,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42024,6 +42978,7 @@
 We can help with hospital website + opd booking. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42070,6 +43025,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42081,6 +43037,7 @@
 We can help with developer site redesign + project pages + lead crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42127,6 +43084,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42138,6 +43096,7 @@
 We can help with full redesign + branch pages + admissions crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42184,6 +43143,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42195,6 +43155,7 @@
 We can help with modern clinic website with implant/rct packages and whatsapp booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42241,6 +43202,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42252,6 +43214,7 @@
 We can help with custom domain website + business email + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42298,6 +43261,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42349,6 +43313,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42360,6 +43325,7 @@
 We can help with maternity + ivf redesign. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42406,6 +43372,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42417,6 +43384,7 @@
 We can help with redesign with mobile booking, whatsapp opd, and specialty service pages.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42463,6 +43431,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42474,6 +43443,7 @@
 We can help with dental clinic redesign with implant/invisalign funnels and online booking.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42520,6 +43490,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42531,6 +43502,7 @@
 We can help with finish brand site, add table booking and events/parties funnel.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42577,6 +43549,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42588,6 +43561,7 @@
 We can help with premium preschool brand site + tour booking + whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42634,6 +43608,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42645,6 +43620,7 @@
 We can help with hotel redesign + booking engine. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42691,6 +43667,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42742,6 +43719,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42753,6 +43731,7 @@
 We can help with premium hospital website + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42799,6 +43778,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42810,6 +43790,7 @@
 We can help with company website + product crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42856,6 +43837,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42867,6 +43849,7 @@
 We can help with export brand website + buyer portal + crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42913,6 +43896,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42964,6 +43948,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -42975,6 +43960,7 @@
 We can help with portfolio redesign + project enquiry crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43021,6 +44007,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43032,6 +44019,7 @@
 We can help with site refresh + online enquiry + student crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43078,6 +44066,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43089,6 +44078,7 @@
 We can help with full website redesign + quote crm. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43135,6 +44125,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43146,6 +44137,7 @@
 We can help with counsellor dashboard + whatsapp admissions + fee enquiry automation. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43192,6 +44184,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43239,6 +44232,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43290,6 +44284,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43301,6 +44296,7 @@
 We can help with local vashi/thane ivf brand polish + whatsapp and paid-lead landing pages.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43347,6 +44343,7 @@
 Regards,
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
@@ -43358,6 +44355,7 @@
 We can help with multi-property booking site with ota-independent reservations.. If useful, I can share a quick redesign concept — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
+hello@dmcstudio.in
 www.dmcstudio.in
 +91 83693 61785</t>
         </is>
